--- a/output/pdf_financials_xlsx/MRE.xlsx
+++ b/output/pdf_financials_xlsx/MRE.xlsx
@@ -2125,31 +2125,31 @@
         <v>4.703</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>4.683</v>
+        <v>1478.039</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>1907.295</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>2559.281</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>2805.165</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>3146.756</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>3347.152</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>3408.74</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>3065.88</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>2954.142</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>0</v>
@@ -2186,31 +2186,31 @@
         <v>-20.237</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>70.827</v>
+        <v>1544.183</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>75.146</v>
+        <v>1982.441</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>49.344</v>
+        <v>2608.625</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>86.369</v>
+        <v>2891.534</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>109.102</v>
+        <v>3255.858</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>136.495</v>
+        <v>3483.647</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>133.339</v>
+        <v>3542.079</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>229.236</v>
+        <v>3295.116</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>246.826</v>
+        <v>3200.968</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>225.045</v>
@@ -2247,31 +2247,31 @@
         <v>-1.77807651079832</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.192487298587232</v>
+        <v>91.40536256221961</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>3.426738004980549</v>
+        <v>90.4014307791718</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1.700928368247683</v>
+        <v>89.92145477910405</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>2.68070111838395</v>
+        <v>89.74676594200717</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>3.031752228963957</v>
+        <v>90.4745536167085</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>3.529947855717341</v>
+        <v>90.09188803784863</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>3.360013224450013</v>
+        <v>89.25694869503053</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>6.211517737845208</v>
+        <v>89.28646234560692</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>6.738540500696169</v>
+        <v>87.38889950585602</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>5.824659991992047</v>
@@ -6553,34 +6553,34 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>4.403</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>4.703</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>44.228</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>55.957</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>73.746</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>99.258</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>110.783</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>124.872</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>136.344</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>149.67</v>
       </c>
       <c r="L100" s="1" t="inlineStr">
         <is>
@@ -7432,31 +7432,31 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>6.072</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>13.857</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>4.066</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>1.647</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>2.677</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.438</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>3.586</v>
       </c>
       <c r="L112" s="1" t="inlineStr">
         <is>
@@ -7489,10 +7489,10 @@
         </is>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>5.383</v>
       </c>
       <c r="S112" s="3" t="n">
-        <v>0</v>
+        <v>0.869</v>
       </c>
     </row>
     <row r="113">
@@ -31078,7 +31078,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -31730,7 +31734,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -38012,7 +38020,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -40646,7 +40654,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -41700,7 +41712,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E322" s="5" t="n">
@@ -47882,7 +47894,11 @@
           <t>Cost of sales (excluding depreciation of property, plant and equipment)</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr">
         <is>
           <t>-</t>
@@ -47894,31 +47910,31 @@
         </is>
       </c>
       <c r="G386" s="5" t="n">
-        <v>-1478.039</v>
+        <v>1478.039</v>
       </c>
       <c r="H386" s="5" t="n">
-        <v>-1907.295</v>
+        <v>1907.295</v>
       </c>
       <c r="I386" s="5" t="n">
-        <v>-2559.281</v>
+        <v>2559.281</v>
       </c>
       <c r="J386" s="5" t="n">
-        <v>-2805.165</v>
+        <v>2805.165</v>
       </c>
       <c r="K386" s="5" t="n">
-        <v>-3146.756</v>
+        <v>3146.756</v>
       </c>
       <c r="L386" s="5" t="n">
-        <v>-3347.152</v>
+        <v>3347.152</v>
       </c>
       <c r="M386" s="5" t="n">
-        <v>-3408.74</v>
+        <v>3408.74</v>
       </c>
       <c r="N386" s="5" t="n">
-        <v>-3065.88</v>
+        <v>3065.88</v>
       </c>
       <c r="O386" s="5" t="n">
-        <v>-2954.142</v>
+        <v>2954.142</v>
       </c>
       <c r="P386" t="inlineStr">
         <is>
@@ -52346,7 +52362,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E431" s="5" t="n">
